--- a/public/templates/new-products-import-template.xlsx
+++ b/public/templates/new-products-import-template.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,18 +28,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00595959"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
@@ -52,6 +41,17 @@
     <font>
       <name val="Arial"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3B57"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00404040"/>
+      <sz val="10.5"/>
     </font>
   </fonts>
   <fills count="3">
@@ -95,20 +95,22 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -474,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -489,357 +491,401 @@
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>New Products import template — fill in the rows below, then use “Upload Excel” in the New Products tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customHeight="1">
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Barcode</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Gross Weight</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Wholesale Price</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>RRP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Name and Code are required for every row. Everything else is optional — leave blank if unknown. Each row is one colour/variant; give variants of the same product a shared Code prefix before the last hyphen (e.g. GSBW-G, GSBW-B) so they group together automatically. Wholesale Price and RRP are both ex-GST, in AUD, numbers only (no $ sign).</t>
+          <t>Wonder max Stroller-Trike - Sage Green</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>WMAX-SAGE</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>smarTrike® Wonder max™ converts from stroller to trike as your toddler grows, with a 3-second fold and carry-on approval for air travel.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>9312345678901</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>189</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="6" t="n"/>
+      <c r="J3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="100" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>How to use this template</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>1. Fill in the “New Products” tab — one row per colour/variant. Delete the example row (row 2) before uploading.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Product Description</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Barcode</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Gross Weight</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Length</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Height</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Wholesale Price</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>RRP</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Wonder max Stroller-Trike - Sage Green</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>WMAX-SAGE</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>smarTrike® Wonder max™ converts from stroller to trike as your toddler grows, with a 3-second fold and carry-on approval for air travel.</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>9312345678901</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>104</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>189</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="n"/>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="8" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="8" t="n"/>
-      <c r="J7" s="8" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="8" t="n"/>
-      <c r="J9" s="8" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="8" t="n"/>
-      <c r="J11" s="8" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="8" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="8" t="n"/>
-      <c r="J13" s="8" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
-      <c r="I14" s="8" t="n"/>
-      <c r="J14" s="8" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="8" t="n"/>
-      <c r="J15" s="8" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="8" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="8" t="n"/>
-      <c r="J17" s="8" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n"/>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="8" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n"/>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="8" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n"/>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="8" t="n"/>
-      <c r="J21" s="8" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="8" t="n"/>
-      <c r="J22" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="8" t="n"/>
-      <c r="J23" s="8" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n"/>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="n"/>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
-      <c r="I25" s="8" t="n"/>
-      <c r="J25" s="8" t="n"/>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>2. Name and Code are required for every row. Everything else is optional — leave blank if unknown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>3. Give variants of the same product a shared Code prefix before the last hyphen (e.g. GSBW-G, GSBW-B) so the dashboard groups them into one product line automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>4. Wholesale Price and RRP are both ex-GST, in AUD, numbers only (no $ sign).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>5. Save the file, then use “Upload Excel” in the New Products tab of the dashboard.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>